--- a/branches/migration/2026.0.1-template-v0.13.2/StructureDefinition-mii-pr-mtb-ploidie.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/StructureDefinition-mii-pr-mtb-ploidie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T15:11:15+00:00</t>
+    <t>2026-09-14T07:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1219,7 +1219,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/genomics-reporting/ValueSet/high-low-codes-vs</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-mtb/ValueSet/mii-vs-mtb-interpretation-high-low</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -2143,7 +2143,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="84.88671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="85.55078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/branches/migration/2026.0.1-template-v0.13.2/StructureDefinition-mii-pr-mtb-ploidie.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/StructureDefinition-mii-pr-mtb-ploidie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:29:46+00:00</t>
+    <t>2026-09-14T08:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/StructureDefinition-mii-pr-mtb-ploidie.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/StructureDefinition-mii-pr-mtb-ploidie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:03:24+00:00</t>
+    <t>2026-09-14T11:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/StructureDefinition-mii-pr-mtb-ploidie.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/StructureDefinition-mii-pr-mtb-ploidie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T11:48:09+00:00</t>
+    <t>2026-09-14T12:20:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/StructureDefinition-mii-pr-mtb-ploidie.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/StructureDefinition-mii-pr-mtb-ploidie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:20:33+00:00</t>
+    <t>2026-09-14T12:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/StructureDefinition-mii-pr-mtb-ploidie.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/StructureDefinition-mii-pr-mtb-ploidie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:53:39+00:00</t>
+    <t>2026-09-14T13:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/StructureDefinition-mii-pr-mtb-ploidie.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/StructureDefinition-mii-pr-mtb-ploidie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:42:50+00:00</t>
+    <t>2026-09-14T17:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
